--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/03 Marzo/tmk/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/09 Septiembre/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_085D08F7534E98DFE54878D6421B66F893559B7A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B4306C51-4C35-4DE7-8B71-69E85897D3C8}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673ED134-0C02-43B1-80A2-38A46D001682}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$87</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="87">
   <si>
     <t>Año</t>
   </si>
@@ -70,18 +86,21 @@
     <t>110.0%</t>
   </si>
   <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>director</t>
+  </si>
+  <si>
+    <t>Raiza Lorena Urzola Lora</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
     <t>0%</t>
   </si>
   <si>
-    <t>director</t>
-  </si>
-  <si>
-    <t>Raiza Lorena Urzola Lora</t>
-  </si>
-  <si>
-    <t>5.0%</t>
-  </si>
-  <si>
     <t>Yessica Yulieth Moreno</t>
   </si>
   <si>
@@ -91,6 +110,15 @@
     <t>Referido - bono</t>
   </si>
   <si>
+    <t>157.5%</t>
+  </si>
+  <si>
+    <t>187.5%</t>
+  </si>
+  <si>
+    <t>117.5%</t>
+  </si>
+  <si>
     <t>Líder</t>
   </si>
   <si>
@@ -100,6 +128,12 @@
     <t>44.2%</t>
   </si>
   <si>
+    <t>92.5%</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
     <t>Pyme Móvil - salarial</t>
   </si>
   <si>
@@ -109,51 +143,33 @@
     <t>CLOUND - salarial</t>
   </si>
   <si>
-    <t>100%</t>
-  </si>
-  <si>
-    <t>157.5%</t>
-  </si>
-  <si>
-    <t>187.5%</t>
-  </si>
-  <si>
-    <t>117.5%</t>
-  </si>
-  <si>
-    <t>92.5%</t>
-  </si>
-  <si>
-    <t>90%</t>
-  </si>
-  <si>
     <t>Febrero</t>
   </si>
   <si>
+    <t>96.0%</t>
+  </si>
+  <si>
+    <t>122.0%</t>
+  </si>
+  <si>
+    <t>68.0%</t>
+  </si>
+  <si>
+    <t>116.0%</t>
+  </si>
+  <si>
+    <t>52.0%</t>
+  </si>
+  <si>
+    <t>104.0%</t>
+  </si>
+  <si>
+    <t>80.7%</t>
+  </si>
+  <si>
     <t>113.3%</t>
   </si>
   <si>
-    <t>80.7%</t>
-  </si>
-  <si>
-    <t>104.0%</t>
-  </si>
-  <si>
-    <t>52.0%</t>
-  </si>
-  <si>
-    <t>116.0%</t>
-  </si>
-  <si>
-    <t>68.0%</t>
-  </si>
-  <si>
-    <t>122.0%</t>
-  </si>
-  <si>
-    <t>96.0%</t>
-  </si>
-  <si>
     <t>Marzo</t>
   </si>
   <si>
@@ -179,6 +195,108 @@
   </si>
   <si>
     <t>158.0%</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>70.0%</t>
+  </si>
+  <si>
+    <t>108.7%</t>
+  </si>
+  <si>
+    <t>64.0%</t>
+  </si>
+  <si>
+    <t>102.0%</t>
+  </si>
+  <si>
+    <t>88.0%</t>
+  </si>
+  <si>
+    <t>114.0%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>Mayo</t>
+  </si>
+  <si>
+    <t>100.7%</t>
+  </si>
+  <si>
+    <t>72.0%</t>
+  </si>
+  <si>
+    <t>76.0%</t>
+  </si>
+  <si>
+    <t>80.0%</t>
+  </si>
+  <si>
+    <t>130.0%</t>
+  </si>
+  <si>
+    <t>Junio</t>
+  </si>
+  <si>
+    <t>106.0%</t>
+  </si>
+  <si>
+    <t>112.0%</t>
+  </si>
+  <si>
+    <t>166.0%</t>
+  </si>
+  <si>
+    <t>48.0%</t>
+  </si>
+  <si>
+    <t>78.0%</t>
+  </si>
+  <si>
+    <t>Julio</t>
+  </si>
+  <si>
+    <t>92.2%</t>
+  </si>
+  <si>
+    <t>108.0%</t>
+  </si>
+  <si>
+    <t>194.0%</t>
+  </si>
+  <si>
+    <t>152.0%</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>94.0%</t>
+  </si>
+  <si>
+    <t>92.0%</t>
+  </si>
+  <si>
+    <t>138.0%</t>
+  </si>
+  <si>
+    <t>93.3%</t>
+  </si>
+  <si>
+    <t>106.7%</t>
+  </si>
+  <si>
+    <t>97.1%</t>
+  </si>
+  <si>
+    <t>Septiembre</t>
   </si>
 </sst>
 </file>
@@ -188,7 +306,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,6 +318,14 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -234,18 +360,21 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -545,12 +674,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -615,7 +744,7 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
         <v>17</v>
@@ -650,7 +779,7 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J3" t="s">
         <v>17</v>
@@ -673,7 +802,7 @@
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>20</v>
@@ -682,10 +811,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J4" t="s">
         <v>17</v>
@@ -702,7 +831,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
@@ -717,10 +846,10 @@
         <v>63</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="I5" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
         <v>17</v>
@@ -737,7 +866,7 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>13</v>
@@ -752,10 +881,10 @@
         <v>75</v>
       </c>
       <c r="H6" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I6" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
         <v>17</v>
@@ -772,13 +901,13 @@
         <v>11</v>
       </c>
       <c r="C7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D7" t="s">
         <v>13</v>
       </c>
       <c r="E7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7">
         <v>40</v>
@@ -787,10 +916,10 @@
         <v>47</v>
       </c>
       <c r="H7" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J7" t="s">
         <v>17</v>
@@ -810,10 +939,10 @@
         <v>12</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F8">
         <v>60</v>
@@ -822,10 +951,10 @@
         <v>26.5</v>
       </c>
       <c r="H8" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J8" t="s">
         <v>17</v>
@@ -842,13 +971,13 @@
         <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F9">
         <v>200</v>
@@ -857,10 +986,10 @@
         <v>185</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="I9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
         <v>17</v>
@@ -877,13 +1006,13 @@
         <v>11</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E10" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F10">
         <v>0</v>
@@ -892,10 +1021,10 @@
         <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J10" t="s">
         <v>17</v>
@@ -912,13 +1041,13 @@
         <v>11</v>
       </c>
       <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" t="s">
         <v>28</v>
-      </c>
-      <c r="D11" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" t="s">
-        <v>24</v>
       </c>
       <c r="F11">
         <v>0</v>
@@ -927,10 +1056,10 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I11" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J11" t="s">
         <v>17</v>
@@ -962,16 +1091,16 @@
         <v>24</v>
       </c>
       <c r="H12" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="I12" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J12" t="s">
         <v>17</v>
       </c>
       <c r="K12" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -982,7 +1111,7 @@
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
         <v>13</v>
@@ -997,16 +1126,16 @@
         <v>61</v>
       </c>
       <c r="H13" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="I13" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J13" t="s">
         <v>17</v>
       </c>
       <c r="K13" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1032,16 +1161,16 @@
         <v>17</v>
       </c>
       <c r="H14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J14" t="s">
         <v>17</v>
       </c>
       <c r="K14" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1052,7 +1181,7 @@
         <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" t="s">
         <v>13</v>
@@ -1067,16 +1196,16 @@
         <v>58</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" t="s">
         <v>17</v>
       </c>
       <c r="K15" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1093,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="E16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F16">
         <v>25</v>
@@ -1102,16 +1231,16 @@
         <v>13</v>
       </c>
       <c r="H16" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J16" t="s">
         <v>17</v>
       </c>
       <c r="K16" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1122,13 +1251,13 @@
         <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" t="s">
         <v>13</v>
       </c>
       <c r="E17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -1137,16 +1266,16 @@
         <v>52</v>
       </c>
       <c r="H17" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I17" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J17" t="s">
         <v>17</v>
       </c>
       <c r="K17" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1160,10 +1289,10 @@
         <v>12</v>
       </c>
       <c r="D18" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E18" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F18">
         <v>75</v>
@@ -1172,16 +1301,16 @@
         <v>60.5</v>
       </c>
       <c r="H18" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J18" t="s">
         <v>17</v>
       </c>
       <c r="K18" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1192,13 +1321,13 @@
         <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F19">
         <v>150</v>
@@ -1207,16 +1336,16 @@
         <v>170</v>
       </c>
       <c r="H19" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="I19" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J19" t="s">
         <v>17</v>
       </c>
       <c r="K19" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1227,13 +1356,13 @@
         <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F20">
         <v>60</v>
@@ -1242,16 +1371,16 @@
         <v>3</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J20" t="s">
         <v>17</v>
       </c>
       <c r="K20" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1262,13 +1391,13 @@
         <v>35</v>
       </c>
       <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>27</v>
+      </c>
+      <c r="E21" t="s">
         <v>28</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21" t="s">
-        <v>24</v>
       </c>
       <c r="F21">
         <v>100000</v>
@@ -1277,16 +1406,16 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J21" t="s">
         <v>17</v>
       </c>
       <c r="K21" s="2">
-        <v>46099.788829440811</v>
+        <v>46099.788829444442</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1300,10 +1429,10 @@
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E22" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F22">
         <v>75</v>
@@ -1315,13 +1444,13 @@
         <v>45</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J22" t="s">
         <v>17</v>
       </c>
       <c r="K22" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1332,13 +1461,13 @@
         <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F23">
         <v>150</v>
@@ -1350,13 +1479,13 @@
         <v>46</v>
       </c>
       <c r="I23" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J23" t="s">
         <v>17</v>
       </c>
       <c r="K23" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1367,13 +1496,13 @@
         <v>44</v>
       </c>
       <c r="C24" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24">
         <v>60</v>
@@ -1382,16 +1511,16 @@
         <v>11</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I24" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J24" t="s">
         <v>17</v>
       </c>
       <c r="K24" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1402,13 +1531,13 @@
         <v>44</v>
       </c>
       <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" t="s">
         <v>28</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" t="s">
-        <v>24</v>
       </c>
       <c r="F25">
         <v>100000</v>
@@ -1417,16 +1546,16 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J25" t="s">
         <v>17</v>
       </c>
       <c r="K25" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1455,13 +1584,13 @@
         <v>47</v>
       </c>
       <c r="I26" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J26" t="s">
         <v>17</v>
       </c>
       <c r="K26" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1472,7 +1601,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D27" t="s">
         <v>13</v>
@@ -1490,13 +1619,13 @@
         <v>48</v>
       </c>
       <c r="I27" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J27" t="s">
         <v>17</v>
       </c>
       <c r="K27" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1525,13 +1654,13 @@
         <v>49</v>
       </c>
       <c r="I28" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J28" t="s">
         <v>17</v>
       </c>
       <c r="K28" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1542,7 +1671,7 @@
         <v>44</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D29" t="s">
         <v>13</v>
@@ -1560,13 +1689,13 @@
         <v>50</v>
       </c>
       <c r="I29" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="J29" t="s">
         <v>17</v>
       </c>
       <c r="K29" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1583,7 +1712,7 @@
         <v>13</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F30">
         <v>25</v>
@@ -1595,13 +1724,13 @@
         <v>51</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s">
         <v>17</v>
       </c>
       <c r="K30" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -1612,13 +1741,13 @@
         <v>44</v>
       </c>
       <c r="C31" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
         <v>13</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F31">
         <v>50</v>
@@ -1630,16 +1759,1985 @@
         <v>52</v>
       </c>
       <c r="I31" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s">
         <v>17</v>
       </c>
       <c r="K31" s="2">
-        <v>46135.554853843933</v>
+        <v>46135.554853842586</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2026</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="C32" t="s">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+      <c r="F32">
+        <v>75</v>
+      </c>
+      <c r="G32">
+        <v>52.5</v>
+      </c>
+      <c r="H32" t="s">
+        <v>54</v>
+      </c>
+      <c r="I32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>2026</v>
+      </c>
+      <c r="B33" t="s">
+        <v>53</v>
+      </c>
+      <c r="C33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" t="s">
+        <v>27</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F33">
+        <v>150</v>
+      </c>
+      <c r="G33">
+        <v>163</v>
+      </c>
+      <c r="H33" t="s">
+        <v>55</v>
+      </c>
+      <c r="I33" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>2026</v>
+      </c>
+      <c r="B34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C34" t="s">
+        <v>32</v>
+      </c>
+      <c r="D34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+      <c r="F34">
+        <v>60</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="H34" t="s">
+        <v>20</v>
+      </c>
+      <c r="I34" t="s">
+        <v>16</v>
+      </c>
+      <c r="J34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>2026</v>
+      </c>
+      <c r="B35" t="s">
+        <v>53</v>
+      </c>
+      <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" t="s">
+        <v>27</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+      <c r="F35">
+        <v>100000</v>
+      </c>
+      <c r="G35">
+        <v>2153085</v>
+      </c>
+      <c r="H35" t="s">
+        <v>20</v>
+      </c>
+      <c r="I35" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>2026</v>
+      </c>
+      <c r="B36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C36" t="s">
+        <v>12</v>
+      </c>
+      <c r="D36" t="s">
+        <v>13</v>
+      </c>
+      <c r="E36" t="s">
+        <v>14</v>
+      </c>
+      <c r="F36">
+        <v>25</v>
+      </c>
+      <c r="G36">
+        <v>16</v>
+      </c>
+      <c r="H36" t="s">
+        <v>56</v>
+      </c>
+      <c r="I36" t="s">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>2026</v>
+      </c>
+      <c r="B37" t="s">
+        <v>53</v>
+      </c>
+      <c r="C37" t="s">
+        <v>23</v>
+      </c>
+      <c r="D37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E37" t="s">
+        <v>14</v>
+      </c>
+      <c r="F37">
+        <v>50</v>
+      </c>
+      <c r="G37">
+        <v>51</v>
+      </c>
+      <c r="H37" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" t="s">
+        <v>20</v>
+      </c>
+      <c r="J37" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>2026</v>
+      </c>
+      <c r="B38" t="s">
+        <v>53</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38">
+        <v>25</v>
+      </c>
+      <c r="G38">
+        <v>22</v>
+      </c>
+      <c r="H38" t="s">
+        <v>58</v>
+      </c>
+      <c r="I38" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>2026</v>
+      </c>
+      <c r="B39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" t="s">
+        <v>23</v>
+      </c>
+      <c r="D39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E39" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39">
+        <v>50</v>
+      </c>
+      <c r="G39">
+        <v>57</v>
+      </c>
+      <c r="H39" t="s">
+        <v>59</v>
+      </c>
+      <c r="I39" t="s">
+        <v>16</v>
+      </c>
+      <c r="J39" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2026</v>
+      </c>
+      <c r="B40" t="s">
+        <v>53</v>
+      </c>
+      <c r="C40" t="s">
+        <v>12</v>
+      </c>
+      <c r="D40" t="s">
+        <v>13</v>
+      </c>
+      <c r="E40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F40">
+        <v>25</v>
+      </c>
+      <c r="G40">
+        <v>10</v>
+      </c>
+      <c r="H40" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" t="s">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2026</v>
+      </c>
+      <c r="B41" t="s">
+        <v>53</v>
+      </c>
+      <c r="C41" t="s">
+        <v>23</v>
+      </c>
+      <c r="D41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E41" t="s">
+        <v>21</v>
+      </c>
+      <c r="F41">
+        <v>50</v>
+      </c>
+      <c r="G41">
+        <v>50</v>
+      </c>
+      <c r="H41" t="s">
+        <v>61</v>
+      </c>
+      <c r="I41" t="s">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41" s="2">
+        <v>46195.587666608793</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2026</v>
+      </c>
+      <c r="B42" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" t="s">
+        <v>12</v>
+      </c>
+      <c r="D42" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" t="s">
+        <v>28</v>
+      </c>
+      <c r="F42">
+        <v>75</v>
+      </c>
+      <c r="G42">
+        <v>75.5</v>
+      </c>
+      <c r="H42" t="s">
+        <v>63</v>
+      </c>
+      <c r="I42" t="s">
+        <v>16</v>
+      </c>
+      <c r="J42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2026</v>
+      </c>
+      <c r="B43" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" t="s">
+        <v>28</v>
+      </c>
+      <c r="F43">
+        <v>150</v>
+      </c>
+      <c r="G43">
+        <v>174</v>
+      </c>
+      <c r="H43" t="s">
+        <v>39</v>
+      </c>
+      <c r="I43" t="s">
+        <v>16</v>
+      </c>
+      <c r="J43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>2026</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" t="s">
+        <v>32</v>
+      </c>
+      <c r="D44" t="s">
+        <v>27</v>
+      </c>
+      <c r="E44" t="s">
+        <v>28</v>
+      </c>
+      <c r="F44">
+        <v>60</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>2026</v>
+      </c>
+      <c r="B45" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" t="s">
+        <v>34</v>
+      </c>
+      <c r="D45" t="s">
+        <v>27</v>
+      </c>
+      <c r="E45" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45">
+        <v>100000</v>
+      </c>
+      <c r="G45">
+        <v>259090</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>2026</v>
+      </c>
+      <c r="B46" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" t="s">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>13</v>
+      </c>
+      <c r="E46" t="s">
+        <v>14</v>
+      </c>
+      <c r="F46">
+        <v>25</v>
+      </c>
+      <c r="G46">
+        <v>18</v>
+      </c>
+      <c r="H46" t="s">
+        <v>64</v>
+      </c>
+      <c r="I46" t="s">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47">
+        <v>2026</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" t="s">
+        <v>23</v>
+      </c>
+      <c r="D47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" t="s">
+        <v>14</v>
+      </c>
+      <c r="F47">
+        <v>50</v>
+      </c>
+      <c r="G47">
+        <v>52</v>
+      </c>
+      <c r="H47" t="s">
+        <v>41</v>
+      </c>
+      <c r="I47" t="s">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>2026</v>
+      </c>
+      <c r="B48" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E48" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48">
+        <v>25</v>
+      </c>
+      <c r="G48">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>65</v>
+      </c>
+      <c r="I48" t="s">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49">
+        <v>2026</v>
+      </c>
+      <c r="B49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" t="s">
+        <v>23</v>
+      </c>
+      <c r="D49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E49" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49">
+        <v>50</v>
+      </c>
+      <c r="G49">
+        <v>57</v>
+      </c>
+      <c r="H49" t="s">
+        <v>59</v>
+      </c>
+      <c r="I49" t="s">
+        <v>16</v>
+      </c>
+      <c r="J49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>2026</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>13</v>
+      </c>
+      <c r="E50" t="s">
+        <v>21</v>
+      </c>
+      <c r="F50">
+        <v>25</v>
+      </c>
+      <c r="G50">
+        <v>20</v>
+      </c>
+      <c r="H50" t="s">
+        <v>66</v>
+      </c>
+      <c r="I50" t="s">
+        <v>16</v>
+      </c>
+      <c r="J50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2026</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" t="s">
+        <v>23</v>
+      </c>
+      <c r="D51" t="s">
+        <v>13</v>
+      </c>
+      <c r="E51" t="s">
+        <v>21</v>
+      </c>
+      <c r="F51">
+        <v>50</v>
+      </c>
+      <c r="G51">
+        <v>65</v>
+      </c>
+      <c r="H51" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" t="s">
+        <v>16</v>
+      </c>
+      <c r="J51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51" s="2">
+        <v>46195.596720196758</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2026</v>
+      </c>
+      <c r="B52" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" t="s">
+        <v>12</v>
+      </c>
+      <c r="D52" t="s">
+        <v>13</v>
+      </c>
+      <c r="E52" t="s">
+        <v>14</v>
+      </c>
+      <c r="F52">
+        <v>25</v>
+      </c>
+      <c r="G52">
+        <v>20</v>
+      </c>
+      <c r="H52" t="s">
+        <v>66</v>
+      </c>
+      <c r="I52" t="s">
+        <v>16</v>
+      </c>
+      <c r="J52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52" s="2">
+        <v>46226.635234062502</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2026</v>
+      </c>
+      <c r="B53" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" t="s">
+        <v>23</v>
+      </c>
+      <c r="D53" t="s">
+        <v>13</v>
+      </c>
+      <c r="E53" t="s">
+        <v>14</v>
+      </c>
+      <c r="F53">
+        <v>50</v>
+      </c>
+      <c r="G53">
+        <v>52</v>
+      </c>
+      <c r="H53" t="s">
+        <v>41</v>
+      </c>
+      <c r="I53" t="s">
+        <v>16</v>
+      </c>
+      <c r="J53" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53" s="2">
+        <v>46226.635234062502</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>2026</v>
+      </c>
+      <c r="B54" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" t="s">
+        <v>12</v>
+      </c>
+      <c r="D54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54">
+        <v>75</v>
+      </c>
+      <c r="G54">
+        <v>75.5</v>
+      </c>
+      <c r="H54" t="s">
+        <v>63</v>
+      </c>
+      <c r="I54" t="s">
+        <v>16</v>
+      </c>
+      <c r="J54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2026</v>
+      </c>
+      <c r="B55" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" t="s">
+        <v>23</v>
+      </c>
+      <c r="D55" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+      <c r="F55">
+        <v>150</v>
+      </c>
+      <c r="G55">
+        <v>159</v>
+      </c>
+      <c r="H55" t="s">
+        <v>69</v>
+      </c>
+      <c r="I55" t="s">
+        <v>16</v>
+      </c>
+      <c r="J55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>2026</v>
+      </c>
+      <c r="B56" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" t="s">
+        <v>32</v>
+      </c>
+      <c r="D56" t="s">
+        <v>27</v>
+      </c>
+      <c r="E56" t="s">
+        <v>28</v>
+      </c>
+      <c r="F56">
+        <v>60</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2026</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" t="s">
+        <v>34</v>
+      </c>
+      <c r="D57" t="s">
+        <v>27</v>
+      </c>
+      <c r="E57" t="s">
+        <v>28</v>
+      </c>
+      <c r="F57">
+        <v>100000</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>2026</v>
+      </c>
+      <c r="B58" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" t="s">
+        <v>12</v>
+      </c>
+      <c r="D58" t="s">
+        <v>13</v>
+      </c>
+      <c r="E58" t="s">
+        <v>14</v>
+      </c>
+      <c r="F58">
+        <v>25</v>
+      </c>
+      <c r="G58">
+        <v>28</v>
+      </c>
+      <c r="H58" t="s">
+        <v>70</v>
+      </c>
+      <c r="I58" t="s">
+        <v>16</v>
+      </c>
+      <c r="J58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59">
+        <v>2026</v>
+      </c>
+      <c r="B59" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" t="s">
+        <v>23</v>
+      </c>
+      <c r="D59" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59">
+        <v>50</v>
+      </c>
+      <c r="G59">
+        <v>83</v>
+      </c>
+      <c r="H59" t="s">
+        <v>71</v>
+      </c>
+      <c r="I59" t="s">
+        <v>16</v>
+      </c>
+      <c r="J59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2026</v>
+      </c>
+      <c r="B60" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" t="s">
+        <v>12</v>
+      </c>
+      <c r="D60" t="s">
+        <v>13</v>
+      </c>
+      <c r="E60" t="s">
+        <v>18</v>
+      </c>
+      <c r="F60">
+        <v>25</v>
+      </c>
+      <c r="G60">
+        <v>12</v>
+      </c>
+      <c r="H60" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" t="s">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61">
+        <v>2026</v>
+      </c>
+      <c r="B61" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" t="s">
+        <v>23</v>
+      </c>
+      <c r="D61" t="s">
+        <v>13</v>
+      </c>
+      <c r="E61" t="s">
+        <v>18</v>
+      </c>
+      <c r="F61">
+        <v>50</v>
+      </c>
+      <c r="G61">
+        <v>38</v>
+      </c>
+      <c r="H61" t="s">
+        <v>65</v>
+      </c>
+      <c r="I61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2026</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>12</v>
+      </c>
+      <c r="D62" t="s">
+        <v>13</v>
+      </c>
+      <c r="E62" t="s">
+        <v>21</v>
+      </c>
+      <c r="F62">
+        <v>25</v>
+      </c>
+      <c r="G62">
+        <v>17</v>
+      </c>
+      <c r="H62" t="s">
+        <v>38</v>
+      </c>
+      <c r="I62" t="s">
+        <v>20</v>
+      </c>
+      <c r="J62" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63">
+        <v>2026</v>
+      </c>
+      <c r="B63" t="s">
+        <v>68</v>
+      </c>
+      <c r="C63" t="s">
+        <v>23</v>
+      </c>
+      <c r="D63" t="s">
+        <v>13</v>
+      </c>
+      <c r="E63" t="s">
+        <v>21</v>
+      </c>
+      <c r="F63">
+        <v>50</v>
+      </c>
+      <c r="G63">
+        <v>39</v>
+      </c>
+      <c r="H63" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" t="s">
+        <v>20</v>
+      </c>
+      <c r="J63" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63" s="2">
+        <v>46226.635931354169</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>2026</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64" t="s">
+        <v>12</v>
+      </c>
+      <c r="D64" t="s">
+        <v>27</v>
+      </c>
+      <c r="E64" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64">
+        <v>45</v>
+      </c>
+      <c r="G64">
+        <v>41.5</v>
+      </c>
+      <c r="H64" t="s">
+        <v>75</v>
+      </c>
+      <c r="I64" t="s">
+        <v>16</v>
+      </c>
+      <c r="J64" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65">
+        <v>2026</v>
+      </c>
+      <c r="B65" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D65" t="s">
+        <v>27</v>
+      </c>
+      <c r="E65" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65">
+        <v>150</v>
+      </c>
+      <c r="G65">
+        <v>171</v>
+      </c>
+      <c r="H65" t="s">
+        <v>59</v>
+      </c>
+      <c r="I65" t="s">
+        <v>16</v>
+      </c>
+      <c r="J65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2026</v>
+      </c>
+      <c r="B66" t="s">
+        <v>74</v>
+      </c>
+      <c r="C66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" t="s">
+        <v>27</v>
+      </c>
+      <c r="E66" t="s">
+        <v>28</v>
+      </c>
+      <c r="F66">
+        <v>60</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66" t="s">
+        <v>20</v>
+      </c>
+      <c r="I66" t="s">
+        <v>20</v>
+      </c>
+      <c r="J66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67">
+        <v>2026</v>
+      </c>
+      <c r="B67" t="s">
+        <v>74</v>
+      </c>
+      <c r="C67" t="s">
+        <v>34</v>
+      </c>
+      <c r="D67" t="s">
+        <v>27</v>
+      </c>
+      <c r="E67" t="s">
+        <v>28</v>
+      </c>
+      <c r="F67">
+        <v>100000</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" t="s">
+        <v>20</v>
+      </c>
+      <c r="J67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68">
+        <v>2026</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+      <c r="D68" t="s">
+        <v>13</v>
+      </c>
+      <c r="E68" t="s">
+        <v>14</v>
+      </c>
+      <c r="F68">
+        <v>25</v>
+      </c>
+      <c r="G68">
+        <v>27</v>
+      </c>
+      <c r="H68" t="s">
+        <v>76</v>
+      </c>
+      <c r="I68" t="s">
+        <v>16</v>
+      </c>
+      <c r="J68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2026</v>
+      </c>
+      <c r="B69" t="s">
+        <v>74</v>
+      </c>
+      <c r="C69" t="s">
+        <v>23</v>
+      </c>
+      <c r="D69" t="s">
+        <v>13</v>
+      </c>
+      <c r="E69" t="s">
+        <v>14</v>
+      </c>
+      <c r="F69">
+        <v>50</v>
+      </c>
+      <c r="G69">
+        <v>97</v>
+      </c>
+      <c r="H69" t="s">
+        <v>77</v>
+      </c>
+      <c r="I69" t="s">
+        <v>16</v>
+      </c>
+      <c r="J69" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2026</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" t="s">
+        <v>12</v>
+      </c>
+      <c r="D70" t="s">
+        <v>13</v>
+      </c>
+      <c r="E70" t="s">
+        <v>21</v>
+      </c>
+      <c r="F70">
+        <v>25</v>
+      </c>
+      <c r="G70">
+        <v>10</v>
+      </c>
+      <c r="H70" t="s">
+        <v>60</v>
+      </c>
+      <c r="I70" t="s">
+        <v>20</v>
+      </c>
+      <c r="J70" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>2026</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" t="s">
+        <v>23</v>
+      </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="E71" t="s">
+        <v>21</v>
+      </c>
+      <c r="F71">
+        <v>50</v>
+      </c>
+      <c r="G71">
+        <v>76</v>
+      </c>
+      <c r="H71" t="s">
+        <v>78</v>
+      </c>
+      <c r="I71" t="s">
+        <v>16</v>
+      </c>
+      <c r="J71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71" s="2">
+        <v>46255.761959166673</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2026</v>
+      </c>
+      <c r="B72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C72" t="s">
+        <v>12</v>
+      </c>
+      <c r="D72" t="s">
+        <v>27</v>
+      </c>
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+      <c r="F72">
+        <v>45</v>
+      </c>
+      <c r="G72">
+        <v>42</v>
+      </c>
+      <c r="H72" t="s">
+        <v>83</v>
+      </c>
+      <c r="I72" t="s">
+        <v>16</v>
+      </c>
+      <c r="J72" t="s">
+        <v>17</v>
+      </c>
+      <c r="K72" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>2026</v>
+      </c>
+      <c r="B73" t="s">
+        <v>79</v>
+      </c>
+      <c r="C73" t="s">
+        <v>23</v>
+      </c>
+      <c r="D73" t="s">
+        <v>27</v>
+      </c>
+      <c r="E73" t="s">
+        <v>28</v>
+      </c>
+      <c r="F73">
+        <v>150</v>
+      </c>
+      <c r="G73">
+        <v>141</v>
+      </c>
+      <c r="H73" t="s">
+        <v>80</v>
+      </c>
+      <c r="I73" t="s">
+        <v>16</v>
+      </c>
+      <c r="J73" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2026</v>
+      </c>
+      <c r="B74" t="s">
+        <v>79</v>
+      </c>
+      <c r="C74" t="s">
+        <v>32</v>
+      </c>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+      <c r="F74">
+        <v>60</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" t="s">
+        <v>20</v>
+      </c>
+      <c r="J74" t="s">
+        <v>17</v>
+      </c>
+      <c r="K74" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75">
+        <v>2026</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>34</v>
+      </c>
+      <c r="D75" t="s">
+        <v>27</v>
+      </c>
+      <c r="E75" t="s">
+        <v>28</v>
+      </c>
+      <c r="F75">
+        <v>100000</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>20</v>
+      </c>
+      <c r="J75" t="s">
+        <v>17</v>
+      </c>
+      <c r="K75" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76">
+        <v>2026</v>
+      </c>
+      <c r="B76" t="s">
+        <v>79</v>
+      </c>
+      <c r="C76" t="s">
+        <v>12</v>
+      </c>
+      <c r="D76" t="s">
+        <v>13</v>
+      </c>
+      <c r="E76" t="s">
+        <v>14</v>
+      </c>
+      <c r="F76">
+        <v>25</v>
+      </c>
+      <c r="G76">
+        <v>23</v>
+      </c>
+      <c r="H76" t="s">
+        <v>81</v>
+      </c>
+      <c r="I76" t="s">
+        <v>16</v>
+      </c>
+      <c r="J76" t="s">
+        <v>17</v>
+      </c>
+      <c r="K76" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>2026</v>
+      </c>
+      <c r="B77" t="s">
+        <v>79</v>
+      </c>
+      <c r="C77" t="s">
+        <v>23</v>
+      </c>
+      <c r="D77" t="s">
+        <v>13</v>
+      </c>
+      <c r="E77" t="s">
+        <v>14</v>
+      </c>
+      <c r="F77">
+        <v>50</v>
+      </c>
+      <c r="G77">
+        <v>69</v>
+      </c>
+      <c r="H77" t="s">
+        <v>82</v>
+      </c>
+      <c r="I77" t="s">
+        <v>16</v>
+      </c>
+      <c r="J77" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78">
+        <v>2026</v>
+      </c>
+      <c r="B78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C78" t="s">
+        <v>12</v>
+      </c>
+      <c r="D78" t="s">
+        <v>13</v>
+      </c>
+      <c r="E78" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78">
+        <v>15</v>
+      </c>
+      <c r="G78">
+        <v>16</v>
+      </c>
+      <c r="H78" t="s">
+        <v>84</v>
+      </c>
+      <c r="I78" t="s">
+        <v>16</v>
+      </c>
+      <c r="J78" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79">
+        <v>2026</v>
+      </c>
+      <c r="B79" t="s">
+        <v>79</v>
+      </c>
+      <c r="C79" t="s">
+        <v>23</v>
+      </c>
+      <c r="D79" t="s">
+        <v>13</v>
+      </c>
+      <c r="E79" t="s">
+        <v>21</v>
+      </c>
+      <c r="F79">
+        <v>70</v>
+      </c>
+      <c r="G79">
+        <v>68</v>
+      </c>
+      <c r="H79" t="s">
+        <v>85</v>
+      </c>
+      <c r="I79" t="s">
+        <v>16</v>
+      </c>
+      <c r="J79" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80">
+        <v>2026</v>
+      </c>
+      <c r="B80" t="s">
+        <v>86</v>
+      </c>
+      <c r="C80" t="s">
+        <v>12</v>
+      </c>
+      <c r="D80" t="s">
+        <v>27</v>
+      </c>
+      <c r="E80" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80">
+        <v>45</v>
+      </c>
+      <c r="G80">
+        <v>46</v>
+      </c>
+      <c r="H80" s="3">
+        <f>G80/F80</f>
+        <v>1.0222222222222221</v>
+      </c>
+      <c r="I80" t="s">
+        <v>20</v>
+      </c>
+      <c r="J80" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81">
+        <v>2026</v>
+      </c>
+      <c r="B81" t="s">
+        <v>86</v>
+      </c>
+      <c r="C81" t="s">
+        <v>23</v>
+      </c>
+      <c r="D81" t="s">
+        <v>27</v>
+      </c>
+      <c r="E81" t="s">
+        <v>28</v>
+      </c>
+      <c r="F81">
+        <v>150</v>
+      </c>
+      <c r="G81">
+        <v>157</v>
+      </c>
+      <c r="H81" s="3">
+        <f t="shared" ref="H81:H87" si="0">G81/F81</f>
+        <v>1.0466666666666666</v>
+      </c>
+      <c r="I81" t="s">
+        <v>20</v>
+      </c>
+      <c r="J81" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82">
+        <v>2026</v>
+      </c>
+      <c r="B82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" t="s">
+        <v>32</v>
+      </c>
+      <c r="D82" t="s">
+        <v>27</v>
+      </c>
+      <c r="E82" t="s">
+        <v>28</v>
+      </c>
+      <c r="F82">
+        <v>60</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I82" t="s">
+        <v>20</v>
+      </c>
+      <c r="J82" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83">
+        <v>2026</v>
+      </c>
+      <c r="B83" t="s">
+        <v>86</v>
+      </c>
+      <c r="C83" t="s">
+        <v>34</v>
+      </c>
+      <c r="D83" t="s">
+        <v>27</v>
+      </c>
+      <c r="E83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F83">
+        <v>100000</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83" s="3">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I83" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84">
+        <v>2026</v>
+      </c>
+      <c r="B84" t="s">
+        <v>86</v>
+      </c>
+      <c r="C84" t="s">
+        <v>12</v>
+      </c>
+      <c r="D84" t="s">
+        <v>13</v>
+      </c>
+      <c r="E84" t="s">
+        <v>14</v>
+      </c>
+      <c r="F84">
+        <v>25</v>
+      </c>
+      <c r="G84">
+        <v>28</v>
+      </c>
+      <c r="H84" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="I84" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85">
+        <v>2026</v>
+      </c>
+      <c r="B85" t="s">
+        <v>86</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="s">
+        <v>14</v>
+      </c>
+      <c r="F85">
+        <v>50</v>
+      </c>
+      <c r="G85">
+        <v>66</v>
+      </c>
+      <c r="H85" s="3">
+        <f t="shared" si="0"/>
+        <v>1.32</v>
+      </c>
+      <c r="I85" t="s">
+        <v>20</v>
+      </c>
+      <c r="J85" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86">
+        <v>2026</v>
+      </c>
+      <c r="B86" t="s">
+        <v>86</v>
+      </c>
+      <c r="C86" t="s">
+        <v>12</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="s">
+        <v>21</v>
+      </c>
+      <c r="F86">
+        <v>15</v>
+      </c>
+      <c r="G86">
+        <v>16</v>
+      </c>
+      <c r="H86" s="3">
+        <f t="shared" si="0"/>
+        <v>1.0666666666666667</v>
+      </c>
+      <c r="I86" t="s">
+        <v>20</v>
+      </c>
+      <c r="J86" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86" s="2">
+        <v>46287.5689004245</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87">
+        <v>2026</v>
+      </c>
+      <c r="B87" t="s">
+        <v>86</v>
+      </c>
+      <c r="C87" t="s">
+        <v>23</v>
+      </c>
+      <c r="D87" t="s">
+        <v>13</v>
+      </c>
+      <c r="E87" t="s">
+        <v>21</v>
+      </c>
+      <c r="F87">
+        <v>70</v>
+      </c>
+      <c r="G87">
+        <v>92</v>
+      </c>
+      <c r="H87" s="3">
+        <f t="shared" si="0"/>
+        <v>1.3142857142857143</v>
+      </c>
+      <c r="I87" t="s">
+        <v>20</v>
+      </c>
+      <c r="J87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87" s="2">
+        <v>46287.5689004245</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K87" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/historico_cambios_TMK.xlsx
+++ b/historico_cambios_TMK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/4 Liquidación TMK/Año 2026/09 Septiembre/tmk/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{673ED134-0C02-43B1-80A2-38A46D001682}"/>
+  <xr:revisionPtr revIDLastSave="37" documentId="8_{A21DB0BB-2ED6-4095-8E6A-528F8E1F0607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B844F86-2FCA-4326-9F9D-0617811E65DD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$87</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$K$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="86">
   <si>
     <t>Año</t>
   </si>
@@ -294,9 +294,6 @@
   </si>
   <si>
     <t>97.1%</t>
-  </si>
-  <si>
-    <t>Septiembre</t>
   </si>
 </sst>
 </file>
@@ -306,7 +303,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,13 +316,6 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -360,21 +350,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -674,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
@@ -3448,296 +3435,8 @@
         <v>46287.5689004245</v>
       </c>
     </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A80">
-        <v>2026</v>
-      </c>
-      <c r="B80" t="s">
-        <v>86</v>
-      </c>
-      <c r="C80" t="s">
-        <v>12</v>
-      </c>
-      <c r="D80" t="s">
-        <v>27</v>
-      </c>
-      <c r="E80" t="s">
-        <v>28</v>
-      </c>
-      <c r="F80">
-        <v>45</v>
-      </c>
-      <c r="G80">
-        <v>46</v>
-      </c>
-      <c r="H80" s="3">
-        <f>G80/F80</f>
-        <v>1.0222222222222221</v>
-      </c>
-      <c r="I80" t="s">
-        <v>20</v>
-      </c>
-      <c r="J80" t="s">
-        <v>17</v>
-      </c>
-      <c r="K80" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81">
-        <v>2026</v>
-      </c>
-      <c r="B81" t="s">
-        <v>86</v>
-      </c>
-      <c r="C81" t="s">
-        <v>23</v>
-      </c>
-      <c r="D81" t="s">
-        <v>27</v>
-      </c>
-      <c r="E81" t="s">
-        <v>28</v>
-      </c>
-      <c r="F81">
-        <v>150</v>
-      </c>
-      <c r="G81">
-        <v>157</v>
-      </c>
-      <c r="H81" s="3">
-        <f t="shared" ref="H81:H87" si="0">G81/F81</f>
-        <v>1.0466666666666666</v>
-      </c>
-      <c r="I81" t="s">
-        <v>20</v>
-      </c>
-      <c r="J81" t="s">
-        <v>17</v>
-      </c>
-      <c r="K81" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82">
-        <v>2026</v>
-      </c>
-      <c r="B82" t="s">
-        <v>86</v>
-      </c>
-      <c r="C82" t="s">
-        <v>32</v>
-      </c>
-      <c r="D82" t="s">
-        <v>27</v>
-      </c>
-      <c r="E82" t="s">
-        <v>28</v>
-      </c>
-      <c r="F82">
-        <v>60</v>
-      </c>
-      <c r="G82">
-        <v>0</v>
-      </c>
-      <c r="H82" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I82" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" t="s">
-        <v>17</v>
-      </c>
-      <c r="K82" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A83">
-        <v>2026</v>
-      </c>
-      <c r="B83" t="s">
-        <v>86</v>
-      </c>
-      <c r="C83" t="s">
-        <v>34</v>
-      </c>
-      <c r="D83" t="s">
-        <v>27</v>
-      </c>
-      <c r="E83" t="s">
-        <v>28</v>
-      </c>
-      <c r="F83">
-        <v>100000</v>
-      </c>
-      <c r="G83">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I83" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" t="s">
-        <v>17</v>
-      </c>
-      <c r="K83" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84">
-        <v>2026</v>
-      </c>
-      <c r="B84" t="s">
-        <v>86</v>
-      </c>
-      <c r="C84" t="s">
-        <v>12</v>
-      </c>
-      <c r="D84" t="s">
-        <v>13</v>
-      </c>
-      <c r="E84" t="s">
-        <v>14</v>
-      </c>
-      <c r="F84">
-        <v>25</v>
-      </c>
-      <c r="G84">
-        <v>28</v>
-      </c>
-      <c r="H84" s="3">
-        <f t="shared" si="0"/>
-        <v>1.1200000000000001</v>
-      </c>
-      <c r="I84" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" t="s">
-        <v>17</v>
-      </c>
-      <c r="K84" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85">
-        <v>2026</v>
-      </c>
-      <c r="B85" t="s">
-        <v>86</v>
-      </c>
-      <c r="C85" t="s">
-        <v>23</v>
-      </c>
-      <c r="D85" t="s">
-        <v>13</v>
-      </c>
-      <c r="E85" t="s">
-        <v>14</v>
-      </c>
-      <c r="F85">
-        <v>50</v>
-      </c>
-      <c r="G85">
-        <v>66</v>
-      </c>
-      <c r="H85" s="3">
-        <f t="shared" si="0"/>
-        <v>1.32</v>
-      </c>
-      <c r="I85" t="s">
-        <v>20</v>
-      </c>
-      <c r="J85" t="s">
-        <v>17</v>
-      </c>
-      <c r="K85" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86">
-        <v>2026</v>
-      </c>
-      <c r="B86" t="s">
-        <v>86</v>
-      </c>
-      <c r="C86" t="s">
-        <v>12</v>
-      </c>
-      <c r="D86" t="s">
-        <v>13</v>
-      </c>
-      <c r="E86" t="s">
-        <v>21</v>
-      </c>
-      <c r="F86">
-        <v>15</v>
-      </c>
-      <c r="G86">
-        <v>16</v>
-      </c>
-      <c r="H86" s="3">
-        <f t="shared" si="0"/>
-        <v>1.0666666666666667</v>
-      </c>
-      <c r="I86" t="s">
-        <v>20</v>
-      </c>
-      <c r="J86" t="s">
-        <v>17</v>
-      </c>
-      <c r="K86" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87">
-        <v>2026</v>
-      </c>
-      <c r="B87" t="s">
-        <v>86</v>
-      </c>
-      <c r="C87" t="s">
-        <v>23</v>
-      </c>
-      <c r="D87" t="s">
-        <v>13</v>
-      </c>
-      <c r="E87" t="s">
-        <v>21</v>
-      </c>
-      <c r="F87">
-        <v>70</v>
-      </c>
-      <c r="G87">
-        <v>92</v>
-      </c>
-      <c r="H87" s="3">
-        <f t="shared" si="0"/>
-        <v>1.3142857142857143</v>
-      </c>
-      <c r="I87" t="s">
-        <v>20</v>
-      </c>
-      <c r="J87" t="s">
-        <v>17</v>
-      </c>
-      <c r="K87" s="2">
-        <v>46287.5689004245</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:K87" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:K79" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>